--- a/hamiltonian_huckel_matrix.xlsx
+++ b/hamiltonian_huckel_matrix.xlsx
@@ -421,7 +421,7 @@
         <v>-56.52499999999999</v>
       </c>
       <c r="B1" t="n">
-        <v>-18.16281386983377</v>
+        <v>-18.16281386983378</v>
       </c>
       <c r="C1" t="n">
         <v>-13.00129679762234</v>
@@ -442,10 +442,10 @@
         <v>-0</v>
       </c>
       <c r="I1" t="n">
-        <v>3.179084241728157e-16</v>
+        <v>3.179084241728158e-16</v>
       </c>
       <c r="J1" t="n">
-        <v>-6.212395791746199e-24</v>
+        <v>-6.2123957917462e-24</v>
       </c>
       <c r="K1" t="n">
         <v>-1.335422066807088e-06</v>
@@ -460,7 +460,7 @@
         <v>-0</v>
       </c>
       <c r="O1" t="n">
-        <v>5.248170616594e-06</v>
+        <v>5.248170616594001e-06</v>
       </c>
       <c r="P1" t="n">
         <v>-0</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-18.16281386983377</v>
+        <v>-18.16281386983378</v>
       </c>
       <c r="B2" t="n">
-        <v>-56.52499999999999</v>
+        <v>-56.52500000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>-59.3515955512911</v>
+        <v>-59.35159555129113</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
@@ -516,7 +516,7 @@
         <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.322440655411209e-15</v>
+        <v>4.322440655411211e-15</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -528,13 +528,13 @@
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.335422066807088e-06</v>
+        <v>-1.335422066807089e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.00583064897382462</v>
+        <v>-0.005830648973824622</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.033268227581024</v>
+        <v>-1.033268227581025</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -552,16 +552,16 @@
         <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.963079500299802</v>
+        <v>2.963079500299803</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7972550147190668</v>
+        <v>-0.7972550147190672</v>
       </c>
       <c r="T2" t="n">
         <v>-13.61387822418404</v>
       </c>
       <c r="U2" t="n">
-        <v>-20.95560497478225</v>
+        <v>-20.95560497478226</v>
       </c>
       <c r="V2" t="n">
         <v>-0</v>
@@ -579,7 +579,7 @@
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>27.94481971328796</v>
+        <v>27.94481971328797</v>
       </c>
     </row>
     <row r="3">
@@ -587,10 +587,10 @@
         <v>-13.00129679762234</v>
       </c>
       <c r="B3" t="n">
-        <v>-59.3515955512911</v>
+        <v>-59.35159555129113</v>
       </c>
       <c r="C3" t="n">
-        <v>-56.52499999999999</v>
+        <v>-56.52500000000001</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
@@ -611,13 +611,13 @@
         <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.08543845540302437</v>
+        <v>-0.0854384554030244</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.033268227581024</v>
+        <v>-1.033268227581025</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.802331136270773</v>
+        <v>-5.802331136270776</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
@@ -626,7 +626,7 @@
         <v>-0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.103213636446229</v>
+        <v>1.10321363644623</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -635,16 +635,16 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>10.61408252188396</v>
+        <v>10.61408252188397</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.086111948358769</v>
+        <v>-5.086111948358773</v>
       </c>
       <c r="T3" t="n">
-        <v>-27.52728889395408</v>
+        <v>-27.52728889395409</v>
       </c>
       <c r="U3" t="n">
-        <v>-39.73323703254574</v>
+        <v>-39.73323703254575</v>
       </c>
       <c r="V3" t="n">
         <v>-0</v>
@@ -653,7 +653,7 @@
         <v>-0</v>
       </c>
       <c r="X3" t="n">
-        <v>20.77544144197767</v>
+        <v>20.77544144197768</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
@@ -662,7 +662,7 @@
         <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>38.38443746423562</v>
+        <v>38.38443746423563</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.9</v>
+        <v>-25.90000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>-0</v>
@@ -730,7 +730,7 @@
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323313</v>
       </c>
       <c r="W4" t="n">
         <v>-0</v>
@@ -739,7 +739,7 @@
         <v>-0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
@@ -762,7 +762,7 @@
         <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>-25.9</v>
+        <v>-25.90000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
@@ -816,7 +816,7 @@
         <v>-0</v>
       </c>
       <c r="W5" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323314</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
@@ -825,7 +825,7 @@
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -836,7 +836,7 @@
         <v>1.392647469931641e-14</v>
       </c>
       <c r="B6" t="n">
-        <v>4.322440655411209e-15</v>
+        <v>4.322440655411211e-15</v>
       </c>
       <c r="C6" t="n">
         <v>-0</v>
@@ -848,7 +848,7 @@
         <v>-0</v>
       </c>
       <c r="F6" t="n">
-        <v>-25.9</v>
+        <v>-25.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
@@ -857,16 +857,16 @@
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-17.86040539558927</v>
+        <v>-17.86040539558928</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.282418925843264e-06</v>
+        <v>-4.282418925843265e-06</v>
       </c>
       <c r="K6" t="n">
         <v>-0.01086013346824452</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.9002037664377227</v>
+        <v>-0.9002037664377229</v>
       </c>
       <c r="M6" t="n">
         <v>-0</v>
@@ -875,7 +875,7 @@
         <v>-0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02052108362380939</v>
+        <v>0.02052108362380941</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
@@ -884,16 +884,16 @@
         <v>-0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.015885950919348</v>
+        <v>2.015885950919349</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.113222974333624</v>
+        <v>-1.113222974333625</v>
       </c>
       <c r="T6" t="n">
-        <v>-9.393473603188916</v>
+        <v>-9.393473603188919</v>
       </c>
       <c r="U6" t="n">
-        <v>-6.198822724479275</v>
+        <v>-6.198822724479278</v>
       </c>
       <c r="V6" t="n">
         <v>-0</v>
@@ -902,7 +902,7 @@
         <v>-0</v>
       </c>
       <c r="X6" t="n">
-        <v>9.694144548168106</v>
+        <v>9.694144548168108</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
@@ -911,7 +911,7 @@
         <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.21131011910405</v>
+        <v>2.211310119104051</v>
       </c>
     </row>
     <row r="7">
@@ -1082,7 +1082,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.179084241728157e-16</v>
+        <v>3.179084241728158e-16</v>
       </c>
       <c r="B9" t="n">
         <v>-0</v>
@@ -1097,7 +1097,7 @@
         <v>-0</v>
       </c>
       <c r="F9" t="n">
-        <v>-17.86040539558927</v>
+        <v>-17.86040539558928</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -1124,7 +1124,7 @@
         <v>-0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.015885950919348</v>
+        <v>2.015885950919349</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -1133,10 +1133,10 @@
         <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>11.13910315775171</v>
+        <v>11.13910315775172</v>
       </c>
       <c r="S9" t="n">
-        <v>-6.639891695782499</v>
+        <v>-6.6398916957825</v>
       </c>
       <c r="T9" t="n">
         <v>-24.69504056554327</v>
@@ -1165,13 +1165,13 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-6.212395791746199e-24</v>
+        <v>-6.2123957917462e-24</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.335422066807088e-06</v>
+        <v>-1.335422066807089e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.08543845540302437</v>
+        <v>-0.0854384554030244</v>
       </c>
       <c r="D10" t="n">
         <v>-0</v>
@@ -1180,7 +1180,7 @@
         <v>-0</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.282418925843264e-06</v>
+        <v>-4.282418925843265e-06</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
@@ -1195,7 +1195,7 @@
         <v>-56.52499999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-18.16281386983377</v>
+        <v>-18.16281386983378</v>
       </c>
       <c r="L10" t="n">
         <v>-13.00129679762234</v>
@@ -1216,7 +1216,7 @@
         <v>-0</v>
       </c>
       <c r="R10" t="n">
-        <v>-3.179084241728157e-16</v>
+        <v>-3.179084241728158e-16</v>
       </c>
       <c r="S10" t="n">
         <v>-0.0004636474705339613</v>
@@ -1251,10 +1251,10 @@
         <v>-1.335422066807088e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00583064897382462</v>
+        <v>-0.005830648973824622</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.033268227581024</v>
+        <v>-1.033268227581025</v>
       </c>
       <c r="D11" t="n">
         <v>-0</v>
@@ -1275,13 +1275,13 @@
         <v>-2.417823020223604</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.16281386983377</v>
+        <v>-18.16281386983378</v>
       </c>
       <c r="K11" t="n">
-        <v>-56.52499999999999</v>
+        <v>-56.52500000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-59.3515955512911</v>
+        <v>-59.35159555129113</v>
       </c>
       <c r="M11" t="n">
         <v>-0</v>
@@ -1290,7 +1290,7 @@
         <v>-0</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.322440655411209e-15</v>
+        <v>-4.322440655411211e-15</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
@@ -1302,13 +1302,13 @@
         <v>-0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7972550147190668</v>
+        <v>-0.7972550147190672</v>
       </c>
       <c r="T11" t="n">
         <v>-13.61387822418404</v>
       </c>
       <c r="U11" t="n">
-        <v>-20.95560497478225</v>
+        <v>-20.95560497478226</v>
       </c>
       <c r="V11" t="n">
         <v>-0</v>
@@ -1326,7 +1326,7 @@
         <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-27.94481971328796</v>
+        <v>-27.94481971328797</v>
       </c>
     </row>
     <row r="12">
@@ -1334,10 +1334,10 @@
         <v>-0.08543845540302437</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.033268227581024</v>
+        <v>-1.033268227581025</v>
       </c>
       <c r="C12" t="n">
-        <v>-5.802331136270773</v>
+        <v>-5.802331136270776</v>
       </c>
       <c r="D12" t="n">
         <v>-0</v>
@@ -1346,7 +1346,7 @@
         <v>-0</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9002037664377227</v>
+        <v>-0.9002037664377229</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -1361,10 +1361,10 @@
         <v>-13.00129679762234</v>
       </c>
       <c r="K12" t="n">
-        <v>-59.3515955512911</v>
+        <v>-59.35159555129113</v>
       </c>
       <c r="L12" t="n">
-        <v>-56.52499999999999</v>
+        <v>-56.52500000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-0</v>
@@ -1385,13 +1385,13 @@
         <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.086111948358769</v>
+        <v>-5.086111948358773</v>
       </c>
       <c r="T12" t="n">
-        <v>-27.52728889395408</v>
+        <v>-27.52728889395409</v>
       </c>
       <c r="U12" t="n">
-        <v>-39.73323703254574</v>
+        <v>-39.73323703254575</v>
       </c>
       <c r="V12" t="n">
         <v>-0</v>
@@ -1400,7 +1400,7 @@
         <v>-0</v>
       </c>
       <c r="X12" t="n">
-        <v>-20.77544144197767</v>
+        <v>-20.77544144197768</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -1409,7 +1409,7 @@
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-38.38443746423562</v>
+        <v>-38.38443746423563</v>
       </c>
     </row>
     <row r="13">
@@ -1450,7 +1450,7 @@
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>-25.9</v>
+        <v>-25.90000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-0</v>
@@ -1477,7 +1477,7 @@
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323313</v>
       </c>
       <c r="W13" t="n">
         <v>-0</v>
@@ -1486,7 +1486,7 @@
         <v>-0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
@@ -1536,7 +1536,7 @@
         <v>-0</v>
       </c>
       <c r="N14" t="n">
-        <v>-25.9</v>
+        <v>-25.90000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323314</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
@@ -1572,7 +1572,7 @@
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
@@ -1580,13 +1580,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5.248170616594e-06</v>
+        <v>5.248170616594001e-06</v>
       </c>
       <c r="B15" t="n">
         <v>0.01330926150554193</v>
       </c>
       <c r="C15" t="n">
-        <v>1.103213636446229</v>
+        <v>1.10321363644623</v>
       </c>
       <c r="D15" t="n">
         <v>-0</v>
@@ -1595,7 +1595,7 @@
         <v>-0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02052108362380939</v>
+        <v>0.02052108362380941</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -1604,13 +1604,13 @@
         <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.015885950919348</v>
+        <v>2.015885950919349</v>
       </c>
       <c r="J15" t="n">
         <v>-1.392647469931641e-14</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.322440655411209e-15</v>
+        <v>-4.322440655411211e-15</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
@@ -1622,7 +1622,7 @@
         <v>-0</v>
       </c>
       <c r="O15" t="n">
-        <v>-25.9</v>
+        <v>-25.90000000000001</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -1631,16 +1631,16 @@
         <v>-0</v>
       </c>
       <c r="R15" t="n">
-        <v>-17.86040539558927</v>
+        <v>-17.86040539558928</v>
       </c>
       <c r="S15" t="n">
-        <v>1.113222974333624</v>
+        <v>1.113222974333625</v>
       </c>
       <c r="T15" t="n">
-        <v>9.393473603188916</v>
+        <v>9.393473603188919</v>
       </c>
       <c r="U15" t="n">
-        <v>6.198822724479275</v>
+        <v>6.198822724479278</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
@@ -1649,7 +1649,7 @@
         <v>-0</v>
       </c>
       <c r="X15" t="n">
-        <v>9.694144548168106</v>
+        <v>9.694144548168108</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
@@ -1658,7 +1658,7 @@
         <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.21131011910405</v>
+        <v>2.211310119104051</v>
       </c>
     </row>
     <row r="16">
@@ -1832,10 +1832,10 @@
         <v>0.30246666190046</v>
       </c>
       <c r="B18" t="n">
-        <v>2.963079500299802</v>
+        <v>2.963079500299803</v>
       </c>
       <c r="C18" t="n">
-        <v>10.61408252188396</v>
+        <v>10.61408252188397</v>
       </c>
       <c r="D18" t="n">
         <v>-0</v>
@@ -1844,7 +1844,7 @@
         <v>-0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.015885950919348</v>
+        <v>2.015885950919349</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
@@ -1853,10 +1853,10 @@
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>11.13910315775171</v>
+        <v>11.13910315775172</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.179084241728157e-16</v>
+        <v>-3.179084241728158e-16</v>
       </c>
       <c r="K18" t="n">
         <v>-0</v>
@@ -1871,7 +1871,7 @@
         <v>-0</v>
       </c>
       <c r="O18" t="n">
-        <v>-17.86040539558927</v>
+        <v>-17.86040539558928</v>
       </c>
       <c r="P18" t="n">
         <v>-0</v>
@@ -1883,7 +1883,7 @@
         <v>-25.9</v>
       </c>
       <c r="S18" t="n">
-        <v>6.639891695782499</v>
+        <v>6.6398916957825</v>
       </c>
       <c r="T18" t="n">
         <v>24.69504056554327</v>
@@ -1915,10 +1915,10 @@
         <v>-0.0004636474705339613</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.7972550147190668</v>
+        <v>-0.7972550147190672</v>
       </c>
       <c r="C19" t="n">
-        <v>-5.086111948358769</v>
+        <v>-5.086111948358773</v>
       </c>
       <c r="D19" t="n">
         <v>-0</v>
@@ -1927,7 +1927,7 @@
         <v>-0</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.113222974333624</v>
+        <v>-1.113222974333625</v>
       </c>
       <c r="G19" t="n">
         <v>-0</v>
@@ -1936,16 +1936,16 @@
         <v>-0</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.639891695782499</v>
+        <v>-6.6398916957825</v>
       </c>
       <c r="J19" t="n">
         <v>-0.0004636474705339613</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7972550147190668</v>
+        <v>-0.7972550147190672</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.086111948358769</v>
+        <v>-5.086111948358773</v>
       </c>
       <c r="M19" t="n">
         <v>-0</v>
@@ -1954,7 +1954,7 @@
         <v>-0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.113222974333624</v>
+        <v>1.113222974333625</v>
       </c>
       <c r="P19" t="n">
         <v>-0</v>
@@ -1963,7 +1963,7 @@
         <v>-0</v>
       </c>
       <c r="R19" t="n">
-        <v>6.639891695782499</v>
+        <v>6.6398916957825</v>
       </c>
       <c r="S19" t="n">
         <v>-37.45</v>
@@ -2001,7 +2001,7 @@
         <v>-13.61387822418404</v>
       </c>
       <c r="C20" t="n">
-        <v>-27.52728889395408</v>
+        <v>-27.52728889395409</v>
       </c>
       <c r="D20" t="n">
         <v>-0</v>
@@ -2010,7 +2010,7 @@
         <v>-0</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.393473603188916</v>
+        <v>-9.393473603188919</v>
       </c>
       <c r="G20" t="n">
         <v>-0</v>
@@ -2028,7 +2028,7 @@
         <v>-13.61387822418404</v>
       </c>
       <c r="L20" t="n">
-        <v>-27.52728889395408</v>
+        <v>-27.52728889395409</v>
       </c>
       <c r="M20" t="n">
         <v>-0</v>
@@ -2037,7 +2037,7 @@
         <v>-0</v>
       </c>
       <c r="O20" t="n">
-        <v>9.393473603188916</v>
+        <v>9.393473603188919</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
@@ -2081,10 +2081,10 @@
         <v>-3.685936488478895</v>
       </c>
       <c r="B21" t="n">
-        <v>-20.95560497478225</v>
+        <v>-20.95560497478226</v>
       </c>
       <c r="C21" t="n">
-        <v>-39.73323703254574</v>
+        <v>-39.73323703254575</v>
       </c>
       <c r="D21" t="n">
         <v>-0</v>
@@ -2093,7 +2093,7 @@
         <v>-0</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.198822724479275</v>
+        <v>-6.198822724479278</v>
       </c>
       <c r="G21" t="n">
         <v>-0</v>
@@ -2108,10 +2108,10 @@
         <v>-3.685936488478895</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.95560497478225</v>
+        <v>-20.95560497478226</v>
       </c>
       <c r="L21" t="n">
-        <v>-39.73323703254574</v>
+        <v>-39.73323703254575</v>
       </c>
       <c r="M21" t="n">
         <v>-0</v>
@@ -2120,7 +2120,7 @@
         <v>-0</v>
       </c>
       <c r="O21" t="n">
-        <v>6.198822724479275</v>
+        <v>6.198822724479278</v>
       </c>
       <c r="P21" t="n">
         <v>-0</v>
@@ -2170,7 +2170,7 @@
         <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323313</v>
       </c>
       <c r="E22" t="n">
         <v>-0</v>
@@ -2197,7 +2197,7 @@
         <v>-0</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323313</v>
       </c>
       <c r="N22" t="n">
         <v>-0</v>
@@ -2256,7 +2256,7 @@
         <v>-0</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323314</v>
       </c>
       <c r="F23" t="n">
         <v>-0</v>
@@ -2283,7 +2283,7 @@
         <v>-0</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.487133180323312</v>
+        <v>-3.487133180323314</v>
       </c>
       <c r="O23" t="n">
         <v>-0</v>
@@ -2333,7 +2333,7 @@
         <v>18.3327334871039</v>
       </c>
       <c r="C24" t="n">
-        <v>20.77544144197767</v>
+        <v>20.77544144197768</v>
       </c>
       <c r="D24" t="n">
         <v>-0</v>
@@ -2342,7 +2342,7 @@
         <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>9.694144548168106</v>
+        <v>9.694144548168108</v>
       </c>
       <c r="G24" t="n">
         <v>-0</v>
@@ -2360,7 +2360,7 @@
         <v>-18.3327334871039</v>
       </c>
       <c r="L24" t="n">
-        <v>-20.77544144197767</v>
+        <v>-20.77544144197768</v>
       </c>
       <c r="M24" t="n">
         <v>-0</v>
@@ -2369,7 +2369,7 @@
         <v>-0</v>
       </c>
       <c r="O24" t="n">
-        <v>9.694144548168106</v>
+        <v>9.694144548168108</v>
       </c>
       <c r="P24" t="n">
         <v>-0</v>
@@ -2419,7 +2419,7 @@
         <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="E25" t="n">
         <v>-0</v>
@@ -2446,7 +2446,7 @@
         <v>-0</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="N25" t="n">
         <v>-0</v>
@@ -2482,7 +2482,7 @@
         <v>-0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-19.95</v>
+        <v>-19.95000000000001</v>
       </c>
       <c r="Z25" t="n">
         <v>-0</v>
@@ -2505,7 +2505,7 @@
         <v>-0</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="F26" t="n">
         <v>-0</v>
@@ -2532,7 +2532,7 @@
         <v>-0</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.429050807371747</v>
+        <v>-5.42905080737175</v>
       </c>
       <c r="O26" t="n">
         <v>-0</v>
@@ -2568,7 +2568,7 @@
         <v>-0</v>
       </c>
       <c r="Z26" t="n">
-        <v>-19.95</v>
+        <v>-19.95000000000001</v>
       </c>
       <c r="AA26" t="n">
         <v>-0</v>
@@ -2579,10 +2579,10 @@
         <v>5.670649251869231</v>
       </c>
       <c r="B27" t="n">
-        <v>27.94481971328796</v>
+        <v>27.94481971328797</v>
       </c>
       <c r="C27" t="n">
-        <v>38.38443746423562</v>
+        <v>38.38443746423563</v>
       </c>
       <c r="D27" t="n">
         <v>-0</v>
@@ -2591,7 +2591,7 @@
         <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>2.21131011910405</v>
+        <v>2.211310119104051</v>
       </c>
       <c r="G27" t="n">
         <v>-0</v>
@@ -2606,10 +2606,10 @@
         <v>-5.670649251869231</v>
       </c>
       <c r="K27" t="n">
-        <v>-27.94481971328796</v>
+        <v>-27.94481971328797</v>
       </c>
       <c r="L27" t="n">
-        <v>-38.38443746423562</v>
+        <v>-38.38443746423563</v>
       </c>
       <c r="M27" t="n">
         <v>-0</v>
@@ -2618,7 +2618,7 @@
         <v>-0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.21131011910405</v>
+        <v>2.211310119104051</v>
       </c>
       <c r="P27" t="n">
         <v>-0</v>
